--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20222.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="43">
   <si>
     <t>Mat</t>
   </si>
@@ -77,6 +77,75 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CALOCA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>EDNA YOSSELIN</t>
+  </si>
+  <si>
+    <t>LESLY VIANEY</t>
+  </si>
+  <si>
+    <t>ARLETH MARELY</t>
+  </si>
+  <si>
+    <t>LLUVIA RUBI</t>
+  </si>
+  <si>
+    <t>TONALLI</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>JULIO</t>
+  </si>
+  <si>
+    <t>DULCE REGINA</t>
   </si>
 </sst>
 </file>
@@ -776,7 +845,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -806,6 +875,190 @@
         <v>19</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>22330051920383</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920155</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920381</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920163</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920299</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920164</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920170</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920287</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20222.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="52">
   <si>
     <t>Mat</t>
   </si>
@@ -79,6 +79,15 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
     <t>CASTELLANOS</t>
   </si>
   <si>
@@ -103,6 +112,15 @@
     <t>VELASCO</t>
   </si>
   <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>CHICO</t>
   </si>
   <si>
@@ -122,6 +140,15 @@
   </si>
   <si>
     <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>FRIDA SOFIA</t>
   </si>
   <si>
     <t>EDNA YOSSELIN</t>
@@ -845,7 +872,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -877,16 +904,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920383</v>
+        <v>22330051920386</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -900,16 +927,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920155</v>
+        <v>22330051920172</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -923,16 +950,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920381</v>
+        <v>22330051920175</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -946,16 +973,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920163</v>
+        <v>22330051920383</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -964,21 +991,21 @@
         <v>11</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920299</v>
+        <v>22330051920155</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -987,21 +1014,21 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920164</v>
+        <v>22330051920381</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1010,21 +1037,21 @@
         <v>11</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920170</v>
+        <v>22330051920163</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1033,21 +1060,21 @@
         <v>11</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920287</v>
+        <v>22330051920299</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1056,7 +1083,76 @@
         <v>11</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920164</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920170</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920287</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20222.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="55">
   <si>
     <t>Mat</t>
   </si>
@@ -79,6 +79,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
@@ -88,7 +91,7 @@
     <t>VALENCIA</t>
   </si>
   <si>
-    <t>CASTELLANOS</t>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>CASTRO</t>
@@ -112,6 +115,9 @@
     <t>VELASCO</t>
   </si>
   <si>
+    <t>CHICO</t>
+  </si>
+  <si>
     <t>LUNA</t>
   </si>
   <si>
@@ -121,7 +127,7 @@
     <t>CERON</t>
   </si>
   <si>
-    <t>CHICO</t>
+    <t>IXTLA</t>
   </si>
   <si>
     <t>MONTIEL</t>
@@ -142,6 +148,9 @@
     <t>SAN JUAN</t>
   </si>
   <si>
+    <t>EDNA YOSSELIN</t>
+  </si>
+  <si>
     <t>GUSTAVO</t>
   </si>
   <si>
@@ -151,7 +160,7 @@
     <t>FRIDA SOFIA</t>
   </si>
   <si>
-    <t>EDNA YOSSELIN</t>
+    <t>ELIEL</t>
   </si>
   <si>
     <t>LESLY VIANEY</t>
@@ -690,16 +699,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>56.41</v>
+      </c>
+      <c r="H2">
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -713,16 +725,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>92.86</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -736,16 +751,19 @@
         <v>20</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="H4">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -810,7 +828,7 @@
         <v>56.41</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -836,7 +854,7 @@
         <v>92.86</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -853,16 +871,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -872,7 +890,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -904,16 +922,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920386</v>
+        <v>22330051920383</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -927,16 +945,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920172</v>
+        <v>22330051920386</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -950,16 +968,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920175</v>
+        <v>22330051920172</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -973,16 +991,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920383</v>
+        <v>22330051920175</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -991,44 +1009,44 @@
         <v>11</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920155</v>
+        <v>20330051920345</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920381</v>
+        <v>22330051920155</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1042,16 +1060,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920163</v>
+        <v>22330051920381</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1065,16 +1083,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920299</v>
+        <v>22330051920163</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1088,16 +1106,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920164</v>
+        <v>22330051920299</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1111,16 +1129,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920170</v>
+        <v>22330051920164</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1134,16 +1152,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920287</v>
+        <v>22330051920170</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1152,6 +1170,29 @@
         <v>11</v>
       </c>
       <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920287</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20222.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="49">
   <si>
     <t>Mat</t>
   </si>
@@ -79,10 +79,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
   </si>
   <si>
     <t>ROJAS</t>
@@ -91,6 +94,9 @@
     <t>VALENCIA</t>
   </si>
   <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -100,25 +106,13 @@
     <t>CALOCA</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>LUNA</t>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
   </si>
   <si>
     <t>ANGUIANO</t>
@@ -127,6 +121,9 @@
     <t>CERON</t>
   </si>
   <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
     <t>IXTLA</t>
   </si>
   <si>
@@ -136,22 +133,16 @@
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>LEON</t>
-  </si>
-  <si>
     <t>SORIANO</t>
   </si>
   <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>EDNA YOSSELIN</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
+    <t>LLUVIA RUBI</t>
+  </si>
+  <si>
+    <t>TONALLI</t>
+  </si>
+  <si>
+    <t>JULIO</t>
   </si>
   <si>
     <t>LUIS ANGEL</t>
@@ -160,6 +151,9 @@
     <t>FRIDA SOFIA</t>
   </si>
   <si>
+    <t>DULCE REGINA</t>
+  </si>
+  <si>
     <t>ELIEL</t>
   </si>
   <si>
@@ -169,19 +163,7 @@
     <t>ARLETH MARELY</t>
   </si>
   <si>
-    <t>LLUVIA RUBI</t>
-  </si>
-  <si>
-    <t>TONALLI</t>
-  </si>
-  <si>
     <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>JULIO</t>
-  </si>
-  <si>
-    <t>DULCE REGINA</t>
   </si>
 </sst>
 </file>
@@ -890,7 +872,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -922,16 +904,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920383</v>
+        <v>22330051920163</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -945,16 +927,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920386</v>
+        <v>22330051920299</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -968,16 +950,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920172</v>
+        <v>22330051920170</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -991,16 +973,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920175</v>
+        <v>22330051920172</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1014,22 +996,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920345</v>
+        <v>22330051920175</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1037,16 +1019,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920155</v>
+        <v>22330051920287</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1055,44 +1037,44 @@
         <v>11</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920381</v>
+        <v>20330051920345</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920163</v>
+        <v>22330051920155</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1106,16 +1088,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920299</v>
+        <v>22330051920381</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1135,10 +1117,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1147,52 +1129,6 @@
         <v>11</v>
       </c>
       <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920170</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920287</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20222.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="46">
   <si>
     <t>Mat</t>
   </si>
@@ -79,12 +79,21 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CALOCA</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
@@ -97,21 +106,18 @@
     <t>VELASCO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CALOCA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
   </si>
   <si>
     <t>LEON</t>
   </si>
   <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
     <t>ALFONSO</t>
   </si>
   <si>
@@ -124,16 +130,10 @@
     <t>SAN JUAN</t>
   </si>
   <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
+    <t>LESLY VIANEY</t>
+  </si>
+  <si>
+    <t>ARLETH MARELY</t>
   </si>
   <si>
     <t>LLUVIA RUBI</t>
@@ -142,6 +142,9 @@
     <t>TONALLI</t>
   </si>
   <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
     <t>JULIO</t>
   </si>
   <si>
@@ -152,18 +155,6 @@
   </si>
   <si>
     <t>DULCE REGINA</t>
-  </si>
-  <si>
-    <t>ELIEL</t>
-  </si>
-  <si>
-    <t>LESLY VIANEY</t>
-  </si>
-  <si>
-    <t>ARLETH MARELY</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
   </si>
 </sst>
 </file>
@@ -827,16 +818,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>92.86</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -853,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>7.6</v>
@@ -872,7 +863,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -904,16 +895,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920163</v>
+        <v>22330051920155</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -922,12 +913,12 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920299</v>
+        <v>22330051920381</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -936,7 +927,7 @@
         <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -945,21 +936,21 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920170</v>
+        <v>22330051920163</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -968,21 +959,21 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920172</v>
+        <v>22330051920299</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -991,21 +982,21 @@
         <v>11</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920175</v>
+        <v>22330051920164</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1014,21 +1005,21 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920287</v>
+        <v>22330051920170</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1037,44 +1028,44 @@
         <v>11</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920345</v>
+        <v>22330051920172</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920155</v>
+        <v>22330051920175</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1088,16 +1079,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920381</v>
+        <v>22330051920287</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1106,29 +1097,6 @@
         <v>11</v>
       </c>
       <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920164</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20222.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -77,84 +77,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CALOCA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>LESLY VIANEY</t>
-  </si>
-  <si>
-    <t>ARLETH MARELY</t>
-  </si>
-  <si>
-    <t>LLUVIA RUBI</t>
-  </si>
-  <si>
-    <t>TONALLI</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>JULIO</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>FRIDA SOFIA</t>
-  </si>
-  <si>
-    <t>DULCE REGINA</t>
   </si>
 </sst>
 </file>
@@ -792,16 +714,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>56.41</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -863,7 +785,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -893,213 +815,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920155</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920381</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920163</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920299</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920164</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920170</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920172</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920175</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920287</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
